--- a/public/downloads/BothraSodium2024.xlsx
+++ b/public/downloads/BothraSodium2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>Se</t>
@@ -656,10 +679,10 @@
         <v>26</v>
       </c>
       <c r="N3" s="5">
-        <v>122.8093059062958</v>
+        <v>122809.3059062958</v>
       </c>
       <c r="O3" s="4">
-        <v>0.0361310108579864</v>
+        <v>36.1310108579864</v>
       </c>
       <c r="P3" s="5">
         <v>3399</v>
@@ -706,10 +729,10 @@
         <v>26</v>
       </c>
       <c r="N4" s="5">
-        <v>290.4816863536835</v>
+        <v>290481.6863536835</v>
       </c>
       <c r="O4" s="4">
-        <v>0.09385514906419498</v>
+        <v>93.85514906419498</v>
       </c>
       <c r="P4" s="5">
         <v>3095</v>
@@ -756,10 +779,10 @@
         <v>26</v>
       </c>
       <c r="N5" s="5">
-        <v>491.2760474681854</v>
+        <v>491276.0474681854</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1480639082182596</v>
+        <v>148.0639082182596</v>
       </c>
       <c r="P5" s="5">
         <v>3318</v>
@@ -806,10 +829,10 @@
         <v>26</v>
       </c>
       <c r="N6" s="5">
-        <v>301.8803579807281</v>
+        <v>301880.3579807281</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09875052599958395</v>
+        <v>98.75052599958394</v>
       </c>
       <c r="P6" s="5">
         <v>3057</v>
@@ -856,10 +879,10 @@
         <v>26</v>
       </c>
       <c r="N7" s="5">
-        <v>960.9672834873199</v>
+        <v>960967.2834873199</v>
       </c>
       <c r="O7" s="4">
-        <v>0.423706915117866</v>
+        <v>423.7069151178659</v>
       </c>
       <c r="P7" s="5">
         <v>2268</v>
@@ -906,10 +929,10 @@
         <v>26</v>
       </c>
       <c r="N8" s="5">
-        <v>84.22004580497742</v>
+        <v>84220.04580497742</v>
       </c>
       <c r="O8" s="4">
-        <v>0.0279893804602783</v>
+        <v>27.9893804602783</v>
       </c>
       <c r="P8" s="5">
         <v>3009</v>
@@ -956,10 +979,10 @@
         <v>26</v>
       </c>
       <c r="N9" s="5">
-        <v>126.0792641639709</v>
+        <v>126079.2641639709</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03848573387178601</v>
+        <v>38.485733871786</v>
       </c>
       <c r="P9" s="5">
         <v>3276</v>
@@ -1006,10 +1029,10 @@
         <v>26</v>
       </c>
       <c r="N10" s="5">
-        <v>308.0746269226074</v>
+        <v>308074.6269226074</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1104210132339095</v>
+        <v>110.4210132339095</v>
       </c>
       <c r="P10" s="5">
         <v>2790</v>
@@ -1056,10 +1079,10 @@
         <v>26</v>
       </c>
       <c r="N11" s="5">
-        <v>141.1085715293884</v>
+        <v>141108.5715293884</v>
       </c>
       <c r="O11" s="4">
-        <v>0.05030608610673384</v>
+        <v>50.30608610673384</v>
       </c>
       <c r="P11" s="5">
         <v>2805</v>
@@ -1106,10 +1129,10 @@
         <v>26</v>
       </c>
       <c r="N12" s="5">
-        <v>77.54326200485229</v>
+        <v>77543.26200485229</v>
       </c>
       <c r="O12" s="4">
-        <v>0.03086913296371508</v>
+        <v>30.86913296371509</v>
       </c>
       <c r="P12" s="5">
         <v>2512</v>
@@ -1156,10 +1179,10 @@
         <v>26</v>
       </c>
       <c r="N13" s="5">
-        <v>227.7668886184692</v>
+        <v>227766.8886184692</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07739275861993518</v>
+        <v>77.39275861993518</v>
       </c>
       <c r="P13" s="5">
         <v>2943</v>
@@ -1206,10 +1229,10 @@
         <v>26</v>
       </c>
       <c r="N14" s="5">
-        <v>4824.679204940796</v>
+        <v>4824679.204940796</v>
       </c>
       <c r="O14" s="4">
-        <v>0.6111056624370862</v>
+        <v>611.1056624370862</v>
       </c>
       <c r="P14" s="5">
         <v>7895</v>
@@ -1256,10 +1279,10 @@
         <v>26</v>
       </c>
       <c r="N15" s="5">
-        <v>1089.402896881104</v>
+        <v>1089402.896881104</v>
       </c>
       <c r="O15" s="4">
-        <v>0.6002219817526742</v>
+        <v>600.2219817526742</v>
       </c>
       <c r="P15" s="5">
         <v>1815</v>
@@ -1306,10 +1329,10 @@
         <v>26</v>
       </c>
       <c r="N16" s="5">
-        <v>1623.392597198486</v>
+        <v>1623392.597198486</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1143153719596146</v>
+        <v>114.3153719596146</v>
       </c>
       <c r="P16" s="5">
         <v>14201</v>
@@ -1356,10 +1379,10 @@
         <v>26</v>
       </c>
       <c r="N17" s="5">
-        <v>306.0381360054016</v>
+        <v>306038.1360054016</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1151818351544605</v>
+        <v>115.1818351544605</v>
       </c>
       <c r="P17" s="5">
         <v>2657</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,25 +1494,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8756337273856243</v>
+        <v>1.060347253793153</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7392952386566124</v>
+        <v>0.613340210387513</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6163815998636099</v>
+        <v>0.8104533460561685</v>
       </c>
       <c r="E3" s="4">
-        <v>89.38137755102041</v>
+        <v>89.01147959183673</v>
       </c>
       <c r="F3" s="4">
-        <v>87.79991610738254</v>
+        <v>86.30872483221476</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
@@ -1484,10 +1539,10 @@
         <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -1496,27 +1551,45 @@
         <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.053278030346266</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8234014464119161</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6485051439946194</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2595952901440402</v>
+        <v>0.3176482029176537</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2595952901440402</v>
+        <v>0.3176482029176537</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1601475717860699</v>
+        <v>0.3203966463601038</v>
       </c>
       <c r="E4" s="4">
-        <v>92.95918367346938</v>
+        <v>91.29591836734694</v>
       </c>
       <c r="F4" s="4">
-        <v>91.8993288590604</v>
+        <v>88.7751677852349</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -1539,9 +1612,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.03084670616731948</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3176482029176537</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3176482029176537</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,66 +1735,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.360882627931957</v>
+        <v>1.465988608603084</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8911295074043531</v>
+        <v>0.8030006521713858</v>
       </c>
       <c r="D3" s="4">
-        <v>1.023188897579274</v>
+        <v>1.223323402214376</v>
       </c>
       <c r="E3" s="4">
-        <v>88.8329081632653</v>
+        <v>87.32142857142857</v>
       </c>
       <c r="F3" s="4">
-        <v>88.19630872483222</v>
+        <v>86.55830536912751</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
         <v>4</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.492055963486613</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9883121027419131</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8795036669591835</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2191469475156168</v>
+        <v>0.3713991447812418</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2191469475156168</v>
+        <v>0.3713991447812418</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3054826324716828</v>
+        <v>0.3662575895639634</v>
       </c>
       <c r="E4" s="4">
-        <v>91.11224489795919</v>
+        <v>88.73469387755102</v>
       </c>
       <c r="F4" s="4">
-        <v>90.25167785234899</v>
+        <v>87.19463087248322</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -1711,9 +1853,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.2054089295918061</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4049256257875004</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4049256257875004</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1884,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1903,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1945,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,25 +1976,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.175427300385337</v>
+        <v>0.8756337273856243</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7044088801838578</v>
+        <v>0.7392952386566124</v>
       </c>
       <c r="D3" s="4">
-        <v>0.827832026370217</v>
+        <v>0.6163815998636099</v>
       </c>
       <c r="E3" s="4">
-        <v>90.36352040816327</v>
+        <v>89.38137755102041</v>
       </c>
       <c r="F3" s="4">
-        <v>90.86059843400449</v>
+        <v>87.79991610738254</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
@@ -1828,10 +2021,10 @@
         <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -1840,27 +2033,45 @@
         <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.693645630845967</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5201710198956375</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.45964293467214</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2513487565571381</v>
+        <v>0.2595952901440402</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2513487565571381</v>
+        <v>0.2595952901440402</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1568891113535187</v>
+        <v>0.1601475717860699</v>
       </c>
       <c r="E4" s="4">
-        <v>94.20748299319729</v>
+        <v>92.95918367346938</v>
       </c>
       <c r="F4" s="4">
-        <v>93.16778523489933</v>
+        <v>91.8993288590604</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -1883,9 +2094,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.2595952901440402</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1588052981947546</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1588052981947546</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2125,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2144,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2186,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,25 +2217,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.227373235342604</v>
+        <v>1.360882627931957</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7335700491962504</v>
+        <v>0.8911295074043531</v>
       </c>
       <c r="D3" s="4">
-        <v>0.988094627349966</v>
+        <v>1.023188897579274</v>
       </c>
       <c r="E3" s="4">
-        <v>89.31760204081633</v>
+        <v>88.8329081632653</v>
       </c>
       <c r="F3" s="4">
-        <v>87.55453020134229</v>
+        <v>88.19630872483222</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
@@ -2014,25 +2276,43 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.333075926655722</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8112473356208442</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6026410932081098</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2491762443906168</v>
+        <v>0.2191469475156168</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2491762443906168</v>
+        <v>0.2191469475156168</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2948224609628937</v>
+        <v>0.3054826324716828</v>
       </c>
       <c r="E4" s="4">
-        <v>91.67346938775511</v>
+        <v>91.11224489795919</v>
       </c>
       <c r="F4" s="4">
-        <v>89.61073825503355</v>
+        <v>90.25167785234899</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -2055,9 +2335,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.0548809754902436</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2191469475156168</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2191469475156168</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2366,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,91 +2458,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.837057420671237</v>
+        <v>1.175427300385337</v>
       </c>
       <c r="C3" s="4">
-        <v>1.005263047178459</v>
+        <v>0.7044088801838578</v>
       </c>
       <c r="D3" s="4">
-        <v>1.631632239952136</v>
+        <v>0.827832026370217</v>
       </c>
       <c r="E3" s="4">
-        <v>74.52806122448979</v>
+        <v>90.36352040816327</v>
       </c>
       <c r="F3" s="4">
-        <v>76.90296420581656</v>
+        <v>90.86059843400449</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.113732906325538</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7599908307071104</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6243368546861916</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.759921718830398</v>
+        <v>0.2513487565571381</v>
       </c>
       <c r="C4" s="4">
-        <v>1.57614694639091</v>
+        <v>0.2513487565571381</v>
       </c>
       <c r="D4" s="4">
-        <v>2.196048570865954</v>
+        <v>0.1568891113535187</v>
       </c>
       <c r="E4" s="4">
-        <v>59.09183673469388</v>
+        <v>94.20748299319729</v>
       </c>
       <c r="F4" s="4">
-        <v>59.89821029082773</v>
+        <v>93.16778523489933</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.2513487565571381</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1466503012489147</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1466503012489147</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2607,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2626,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2668,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,25 +2699,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9757930469088146</v>
+        <v>1.227373235342604</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6088735297635286</v>
+        <v>0.7335700491962504</v>
       </c>
       <c r="D3" s="4">
-        <v>1.200688465555216</v>
+        <v>0.988094627349966</v>
       </c>
       <c r="E3" s="4">
-        <v>92.81887755102041</v>
+        <v>89.31760204081633</v>
       </c>
       <c r="F3" s="4">
-        <v>93.09144295302013</v>
+        <v>87.55453020134229</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
@@ -2358,25 +2758,43 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.157679659105367</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8052225822129232</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5565957313917983</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.146909118885912</v>
+        <v>0.2491762443906168</v>
       </c>
       <c r="C4" s="4">
-        <v>1.146909118885912</v>
+        <v>0.2491762443906168</v>
       </c>
       <c r="D4" s="4">
-        <v>1.64852364181944</v>
+        <v>0.2948224609628937</v>
       </c>
       <c r="E4" s="4">
-        <v>97.93877551020408</v>
+        <v>91.67346938775511</v>
       </c>
       <c r="F4" s="4">
-        <v>95.41610738255034</v>
+        <v>89.61073825503355</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -2399,9 +2817,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1096089112812592</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2491762443906168</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2491762443906168</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2848,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2867,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2909,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,91 +2940,143 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.796593799501927</v>
+        <v>1.837057420671237</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5427516016022869</v>
+        <v>1.005263047178459</v>
       </c>
       <c r="D3" s="4">
-        <v>1.30436744656975</v>
+        <v>1.631632239952136</v>
       </c>
       <c r="E3" s="4">
-        <v>44.01785714285715</v>
+        <v>74.52806122448979</v>
       </c>
       <c r="F3" s="4">
-        <v>49.94546979865772</v>
+        <v>76.90296420581656</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
+        <v>8</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>8</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
         <v>4</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2833850375633412</v>
+      </c>
+      <c r="O3" s="5">
         <v>12</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>10</v>
-      </c>
-      <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>1.766211161280402</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.005263047178459</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6418875467727698</v>
+        <v>1.759921718830398</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>1.57614694639091</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7101615917627295</v>
+        <v>2.196048570865954</v>
       </c>
       <c r="E4" s="4">
-        <v>22.8299319727891</v>
+        <v>59.09183673469388</v>
       </c>
       <c r="F4" s="4">
-        <v>35.1420581655481</v>
+        <v>59.89821029082773</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.759921718830398</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.57614694639091</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3087,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3095,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3106,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3148,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,25 +3179,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9559620820320044</v>
+        <v>0.9757930469088146</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5919013084962287</v>
+        <v>0.6088735297635286</v>
       </c>
       <c r="D3" s="4">
-        <v>1.106043153826049</v>
+        <v>1.200688465555216</v>
       </c>
       <c r="E3" s="4">
-        <v>90.32525510204081</v>
+        <v>92.81887755102041</v>
       </c>
       <c r="F3" s="4">
-        <v>91.19756711409396</v>
+        <v>93.09144295302013</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
@@ -2702,25 +3238,43 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5265941985078182</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.964416397496191</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5428615115922806</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9915670645184596</v>
+        <v>1.146909118885912</v>
       </c>
       <c r="C4" s="4">
-        <v>0.9915670645184596</v>
+        <v>1.146909118885912</v>
       </c>
       <c r="D4" s="4">
-        <v>1.495406080478789</v>
+        <v>1.64852364181944</v>
       </c>
       <c r="E4" s="4">
-        <v>94.39795918367346</v>
+        <v>97.93877551020408</v>
       </c>
       <c r="F4" s="4">
-        <v>92.53020134228188</v>
+        <v>95.41610738255034</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -2743,9 +3297,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-1.146909118885912</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1138818433117392</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1138818433117392</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3328,1346 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.796593799501927</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5427516016022869</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.30436744656975</v>
+      </c>
+      <c r="E3" s="4">
+        <v>44.01785714285715</v>
+      </c>
+      <c r="F3" s="4">
+        <v>49.94546979865772</v>
+      </c>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>12</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>10</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.430337654733407</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.25660398278061</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9573908905643125</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6418875467727698</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>0.7101615917627295</v>
+      </c>
+      <c r="E4" s="4">
+        <v>22.8299319727891</v>
+      </c>
+      <c r="F4" s="4">
+        <v>35.1420581655481</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6418875467727698</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9559620820320044</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5919013084962287</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.106043153826049</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.32525510204081</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91.19756711409396</v>
+      </c>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6640132194496627</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8956960119537681</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4928701813613381</v>
+      </c>
+      <c r="R3" s="5">
+        <v>11</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.9915670645184596</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.9915670645184596</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.495406080478789</v>
+      </c>
+      <c r="E4" s="4">
+        <v>94.39795918367346</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.53020134228188</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.9915670645184596</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.169084116251594</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.169084116251594</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.6179428094020405</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.5315351378397775</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.7608165684920909</v>
+      </c>
+      <c r="K3" s="4">
+        <v>88.38827838827831</v>
+      </c>
+      <c r="L3" s="4">
+        <v>86.76905868180933</v>
+      </c>
+      <c r="M3" s="5">
+        <v>26</v>
+      </c>
+      <c r="N3" s="5">
+        <v>122809.3059062958</v>
+      </c>
+      <c r="O3" s="4">
+        <v>36.1310108579864</v>
+      </c>
+      <c r="P3" s="5">
+        <v>3399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G4" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.6990695666528215</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.5422940330703091</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.7736137501444476</v>
+      </c>
+      <c r="K4" s="4">
+        <v>89.06593406593394</v>
+      </c>
+      <c r="L4" s="4">
+        <v>88.69643779039683</v>
+      </c>
+      <c r="M4" s="5">
+        <v>26</v>
+      </c>
+      <c r="N4" s="5">
+        <v>290481.6863536835</v>
+      </c>
+      <c r="O4" s="4">
+        <v>93.85514906419498</v>
+      </c>
+      <c r="P4" s="5">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G5" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5776357152310818</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.4372828867822519</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.7672130307242093</v>
+      </c>
+      <c r="K5" s="4">
+        <v>90.32182103610661</v>
+      </c>
+      <c r="L5" s="4">
+        <v>88.19437274135205</v>
+      </c>
+      <c r="M5" s="5">
+        <v>26</v>
+      </c>
+      <c r="N5" s="5">
+        <v>491276.0474681854</v>
+      </c>
+      <c r="O5" s="4">
+        <v>148.0639082182596</v>
+      </c>
+      <c r="P5" s="5">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.5458980067533479</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.4516736564209158</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.7042373456442199</v>
+      </c>
+      <c r="K6" s="4">
+        <v>90.61616954474096</v>
+      </c>
+      <c r="L6" s="4">
+        <v>88.851746687317</v>
+      </c>
+      <c r="M6" s="5">
+        <v>26</v>
+      </c>
+      <c r="N6" s="5">
+        <v>301880.3579807281</v>
+      </c>
+      <c r="O6" s="4">
+        <v>98.75052599958394</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.545383655692809</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3891675783963613</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.7530441797016203</v>
+      </c>
+      <c r="K7" s="4">
+        <v>93.23390894819444</v>
+      </c>
+      <c r="L7" s="4">
+        <v>91.66451557391032</v>
+      </c>
+      <c r="M7" s="5">
+        <v>26</v>
+      </c>
+      <c r="N7" s="5">
+        <v>960967.2834873199</v>
+      </c>
+      <c r="O7" s="4">
+        <v>423.7069151178659</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.6288809681448922</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.4981156253232713</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.7590609878660697</v>
+      </c>
+      <c r="K8" s="4">
+        <v>89.89010989010974</v>
+      </c>
+      <c r="L8" s="4">
+        <v>87.25735673722193</v>
+      </c>
+      <c r="M8" s="5">
+        <v>26</v>
+      </c>
+      <c r="N8" s="5">
+        <v>84220.04580497742</v>
+      </c>
+      <c r="O8" s="4">
+        <v>27.9893804602783</v>
+      </c>
+      <c r="P8" s="5">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7639326885286775</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.6731653881888865</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.8168241813723051</v>
+      </c>
+      <c r="K9" s="4">
+        <v>87.86499215070634</v>
+      </c>
+      <c r="L9" s="4">
+        <v>86.80304594734037</v>
+      </c>
+      <c r="M9" s="5">
+        <v>26</v>
+      </c>
+      <c r="N9" s="5">
+        <v>126079.2641639709</v>
+      </c>
+      <c r="O9" s="4">
+        <v>38.485733871786</v>
+      </c>
+      <c r="P9" s="5">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C10" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3811842038568364</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3228985544551466</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3976885117168483</v>
+      </c>
+      <c r="K10" s="4">
+        <v>90.75745682888525</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.37661331956632</v>
+      </c>
+      <c r="M10" s="5">
+        <v>26</v>
+      </c>
+      <c r="N10" s="5">
+        <v>308074.6269226074</v>
+      </c>
+      <c r="O10" s="4">
+        <v>110.4210132339095</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G11" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.5835164171188337</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.4283255724387948</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.7136680599142208</v>
+      </c>
+      <c r="K11" s="4">
+        <v>89.70957613814744</v>
+      </c>
+      <c r="L11" s="4">
+        <v>88.98683531233766</v>
+      </c>
+      <c r="M11" s="5">
+        <v>26</v>
+      </c>
+      <c r="N11" s="5">
+        <v>141108.5715293884</v>
+      </c>
+      <c r="O11" s="4">
+        <v>50.30608610673384</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.5240906270693428</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.4166470488438974</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.7058344794169259</v>
+      </c>
+      <c r="K12" s="4">
+        <v>91.84196755625307</v>
+      </c>
+      <c r="L12" s="4">
+        <v>91.7479779728093</v>
+      </c>
+      <c r="M12" s="5">
+        <v>26</v>
+      </c>
+      <c r="N12" s="5">
+        <v>77543.26200485229</v>
+      </c>
+      <c r="O12" s="4">
+        <v>30.86913296371509</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.5913586061274207</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.4168596009367159</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.6641602908774539</v>
+      </c>
+      <c r="K13" s="4">
+        <v>90.22370486656189</v>
+      </c>
+      <c r="L13" s="4">
+        <v>88.34537945276145</v>
+      </c>
+      <c r="M13" s="5">
+        <v>26</v>
+      </c>
+      <c r="N13" s="5">
+        <v>227766.8886184692</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.39275861993518</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>34.61538461538461</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>65.38461538461539</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>46.15384615384615</v>
+      </c>
+      <c r="G14" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.763792144953477</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1.068694591535398</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1.778258152022378</v>
+      </c>
+      <c r="K14" s="4">
+        <v>68.59105180533709</v>
+      </c>
+      <c r="L14" s="4">
+        <v>70.36267423851241</v>
+      </c>
+      <c r="M14" s="5">
+        <v>26</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4824679.204940796</v>
+      </c>
+      <c r="O14" s="4">
+        <v>611.1056624370862</v>
+      </c>
+      <c r="P14" s="5">
+        <v>7895</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>80.76923076923077</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G15" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.6372877228098635</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3385854790777371</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.987823785723161</v>
+      </c>
+      <c r="K15" s="4">
+        <v>94.78806907378309</v>
+      </c>
+      <c r="L15" s="4">
+        <v>93.98554465668464</v>
+      </c>
+      <c r="M15" s="5">
+        <v>26</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1089402.896881104</v>
+      </c>
+      <c r="O15" s="4">
+        <v>600.2219817526742</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>80.76923076923077</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.635559199700671</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.9573908905643125</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.63667257413143</v>
+      </c>
+      <c r="K16" s="4">
+        <v>35.86865515436944</v>
+      </c>
+      <c r="L16" s="4">
+        <v>44.25184993976902</v>
+      </c>
+      <c r="M16" s="5">
+        <v>26</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1623392.597198486</v>
+      </c>
+      <c r="O16" s="4">
+        <v>114.3153719596146</v>
+      </c>
+      <c r="P16" s="5">
+        <v>14201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>80.76923076923077</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.6162298982221627</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.3386863408328885</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.9407227473411182</v>
+      </c>
+      <c r="K17" s="4">
+        <v>91.89167974882238</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.71011874031916</v>
+      </c>
+      <c r="M17" s="5">
+        <v>26</v>
+      </c>
+      <c r="N17" s="5">
+        <v>306038.1360054016</v>
+      </c>
+      <c r="O17" s="4">
+        <v>115.1818351544605</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2657</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3516,9 +5422,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>22</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>2</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>17</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>12</v>
+      </c>
+      <c r="G14" s="5">
+        <v>5</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>9</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>5</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5">
+        <v>3</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>2</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>20</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>20</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>21</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5">
+        <v>3</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6190,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6232,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,10 +6263,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.14522259704475</v>
@@ -3629,10 +6322,28 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.085338099776988</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8664288909580031</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7708967216299906</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2103022538593791</v>
@@ -3670,9 +6381,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.09438903213086861</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2203650789125004</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2203650789125004</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6412,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6431,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6473,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6504,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.266895118059708</v>
@@ -3801,10 +6563,28 @@
       <c r="M3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.9744903507753732</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9864014082031685</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7947568771520118</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3569814443005385</v>
@@ -3842,9 +6622,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.3527979147380279</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.239338620172266</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.239338620172266</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6653,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6672,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6714,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,10 +6745,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.9464793974929862</v>
@@ -3973,10 +6804,28 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.950875534355589</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7723800665873455</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5799813315499117</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2746221537443375</v>
@@ -4014,9 +6863,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.04288700341638787</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.26604475306106</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.26604475306106</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6894,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6913,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6955,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,10 +6986,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.170449507573949</v>
@@ -4145,10 +7045,28 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.120751491939343</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7369644240562211</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6143520543841201</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.218304746851561</v>
@@ -4186,9 +7104,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1094349610859467</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2401917390687504</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2401917390687504</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7135,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7154,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7196,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7227,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.9751408676081894</v>
@@ -4317,10 +7286,28 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.9476982320080651</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7794787418582416</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.571114295536565</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1745480992797752</v>
@@ -4358,9 +7345,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.1193127882426666</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1708315178281168</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1708315178281168</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7376,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.060347253793153</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.613340210387513</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.8104533460561685</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.01147959183673</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.30872483221476</v>
-      </c>
-      <c r="G3" s="5">
-        <v>16</v>
-      </c>
-      <c r="H3" s="5">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3176482029176537</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3176482029176537</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3203966463601038</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.29591836734694</v>
-      </c>
-      <c r="F4" s="4">
-        <v>88.7751677852349</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.465988608603084</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.8030006521713858</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.223323402214376</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.32142857142857</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.55830536912751</v>
-      </c>
-      <c r="G3" s="5">
-        <v>16</v>
-      </c>
-      <c r="H3" s="5">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>6</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3713991447812418</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3713991447812418</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3662575895639634</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.73469387755102</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.19463087248322</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BothraSodium2024.xlsx
+++ b/public/downloads/BothraSodium2024.xlsx
@@ -1554,16 +1554,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.053278030346266</v>
+        <v>-0.5690075434979587</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8234014464119161</v>
+        <v>0.7410876521547319</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6485051439946194</v>
+        <v>0.3773299227022711</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.03084670616731948</v>
+        <v>-0.0860574114682624</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -1795,16 +1795,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.492055963486613</v>
+        <v>-1.381255084528334</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9883121027419131</v>
+        <v>0.969444395970541</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.8795036669591835</v>
+        <v>0.8648050185450546</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -1854,16 +1854,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2054089295918061</v>
+        <v>-0.04481285637695009</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4049256257875004</v>
+        <v>0.3713991447812418</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4049256257875004</v>
+        <v>0.3713991447812418</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.693645630845967</v>
+        <v>-0.8475574923913394</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5201710198956375</v>
+        <v>0.5073472362931635</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.45964293467214</v>
+        <v>0.4425445565355078</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2095,16 +2095,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2595952901440402</v>
+        <v>0.1982815267531035</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1588052981947546</v>
+        <v>0.1563529451187911</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1588052981947546</v>
+        <v>0.1563529451187911</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -2277,16 +2277,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.333075926655722</v>
+        <v>-0.8134084231086263</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8112473356208442</v>
+        <v>0.7223286889825573</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6026410932081098</v>
+        <v>0.3108603965080287</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0548809754902436</v>
+        <v>0.001365301630869453</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -2518,22 +2518,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.113732906325538</v>
+        <v>-0.7307577591076893</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7599908307071104</v>
+        <v>0.6806779376881238</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6243368546861916</v>
+        <v>0.2883289829568033</v>
       </c>
       <c r="R3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2577,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2513487565571381</v>
+        <v>0.2356491940320211</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1466503012489147</v>
+        <v>0.1464174553281168</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1466503012489147</v>
+        <v>0.1464174553281168</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -2759,16 +2759,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.157679659105367</v>
+        <v>-0.6936399209927799</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8052225822129232</v>
+        <v>0.703407748074099</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5565957313917983</v>
+        <v>0.2661627065025035</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1096089112812592</v>
+        <v>0.0215127213281221</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -3000,13 +3000,13 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2833850375633412</v>
+        <v>0.3139515726173063</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>1.766211161280402</v>
+        <v>1.758569527516911</v>
       </c>
       <c r="Q3" s="4">
         <v>1.005263047178459</v>
@@ -3239,22 +3239,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5265941985078182</v>
+        <v>-0.2815146590135669</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.964416397496191</v>
+        <v>0.9563379878929076</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5428615115922806</v>
+        <v>0.629852560911247</v>
       </c>
       <c r="R3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3298,16 +3298,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.146909118885912</v>
+        <v>-1.192361746520175</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1138818433117392</v>
+        <v>0.1081652447112299</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1138818433117392</v>
+        <v>0.1081652447112299</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3480,16 +3480,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.430337654733407</v>
+        <v>-0.8547569131181945</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>2.25660398278061</v>
+        <v>1.954408429234761</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9573908905643125</v>
+        <v>0.6178407623148049</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3715,22 +3715,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6640132194496627</v>
+        <v>-0.4601124523155544</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8956960119537681</v>
+        <v>0.8678293111149663</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4928701813613381</v>
+        <v>0.5510763559927704</v>
       </c>
       <c r="R3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3774,16 +3774,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9915670645184596</v>
+        <v>-1.053792128394986</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.169084116251594</v>
+        <v>0.1602323814757563</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.169084116251594</v>
+        <v>0.1602323814757563</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3902,13 +3902,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>88.46153846153845</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="C3" s="3">
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>11.53846153846154</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>7.692307692307693</v>
       </c>
       <c r="G3" s="3">
-        <v>3.846153846153846</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H3" s="4">
-        <v>0.6179428094020405</v>
+        <v>0.6135412670296668</v>
       </c>
       <c r="I3" s="4">
-        <v>0.5315351378397775</v>
+        <v>0.3894541801769936</v>
       </c>
       <c r="J3" s="4">
-        <v>0.7608165684920909</v>
+        <v>0.6353236693637515</v>
       </c>
       <c r="K3" s="4">
         <v>88.38827838827831</v>
@@ -3970,13 +3970,13 @@
         <v>7.692307692307693</v>
       </c>
       <c r="H4" s="4">
-        <v>0.6990695666528215</v>
+        <v>0.6792148010892272</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5422940330703091</v>
+        <v>0.518829310131516</v>
       </c>
       <c r="J4" s="4">
-        <v>0.7736137501444476</v>
+        <v>0.7027339855820375</v>
       </c>
       <c r="K4" s="4">
         <v>89.06593406593394</v>
@@ -4020,13 +4020,13 @@
         <v>7.692307692307693</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5776357152310818</v>
+        <v>0.5071347987092517</v>
       </c>
       <c r="I5" s="4">
-        <v>0.4372828867822519</v>
+        <v>0.2548687527241575</v>
       </c>
       <c r="J5" s="4">
-        <v>0.7672130307242093</v>
+        <v>0.5566844349119895</v>
       </c>
       <c r="K5" s="4">
         <v>90.32182103610661</v>
@@ -4052,13 +4052,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>88.46153846153845</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
       </c>
       <c r="D6" s="3">
-        <v>11.53846153846154</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -4067,16 +4067,16 @@
         <v>7.692307692307693</v>
       </c>
       <c r="G6" s="3">
-        <v>3.846153846153846</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H6" s="4">
-        <v>0.5458980067533479</v>
+        <v>0.5036706827895483</v>
       </c>
       <c r="I6" s="4">
-        <v>0.4516736564209158</v>
+        <v>0.2664456062182539</v>
       </c>
       <c r="J6" s="4">
-        <v>0.7042373456442199</v>
+        <v>0.5078969889843236</v>
       </c>
       <c r="K6" s="4">
         <v>90.61616954474096</v>
@@ -4120,13 +4120,13 @@
         <v>7.692307692307693</v>
       </c>
       <c r="H7" s="4">
-        <v>0.545383655692809</v>
+        <v>0.488346404554958</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3891675783963613</v>
+        <v>0.2358539527896203</v>
       </c>
       <c r="J7" s="4">
-        <v>0.7530441797016203</v>
+        <v>0.6072048653070877</v>
       </c>
       <c r="K7" s="4">
         <v>93.23390894819444</v>
@@ -4170,13 +4170,13 @@
         <v>7.692307692307693</v>
       </c>
       <c r="H8" s="4">
-        <v>0.6288809681448922</v>
+        <v>0.5782263255250865</v>
       </c>
       <c r="I8" s="4">
-        <v>0.4981156253232713</v>
+        <v>0.3502018682547177</v>
       </c>
       <c r="J8" s="4">
-        <v>0.7590609878660697</v>
+        <v>0.5876819113665376</v>
       </c>
       <c r="K8" s="4">
         <v>89.89010989010974</v>
@@ -4220,13 +4220,13 @@
         <v>3.846153846153846</v>
       </c>
       <c r="H9" s="4">
-        <v>0.7639326885286775</v>
+        <v>0.7394269916669644</v>
       </c>
       <c r="I9" s="4">
-        <v>0.6731653881888865</v>
+        <v>0.6502807256042665</v>
       </c>
       <c r="J9" s="4">
-        <v>0.8168241813723051</v>
+        <v>0.7805300626118966</v>
       </c>
       <c r="K9" s="4">
         <v>87.86499215070634</v>
@@ -4270,13 +4270,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3811842038568364</v>
+        <v>0.3723494319953279</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3228985544551466</v>
+        <v>0.3124574604370002</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3976885117168483</v>
+        <v>0.415184035332169</v>
       </c>
       <c r="K10" s="4">
         <v>90.75745682888525</v>
@@ -4320,13 +4320,13 @@
         <v>7.692307692307693</v>
       </c>
       <c r="H11" s="4">
-        <v>0.5835164171188337</v>
+        <v>0.528797249956811</v>
       </c>
       <c r="I11" s="4">
-        <v>0.4283255724387948</v>
+        <v>0.2691724651478415</v>
       </c>
       <c r="J11" s="4">
-        <v>0.7136680599142208</v>
+        <v>0.5379132550927946</v>
       </c>
       <c r="K11" s="4">
         <v>89.70957613814744</v>
@@ -4352,13 +4352,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>88.46153846153845</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
       </c>
       <c r="D12" s="3">
-        <v>11.53846153846154</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -4367,16 +4367,16 @@
         <v>7.692307692307693</v>
       </c>
       <c r="G12" s="3">
-        <v>3.846153846153846</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H12" s="4">
-        <v>0.5240906270693428</v>
+        <v>0.4751931367804288</v>
       </c>
       <c r="I12" s="4">
-        <v>0.4166470488438974</v>
+        <v>0.2238237431255822</v>
       </c>
       <c r="J12" s="4">
-        <v>0.7058344794169259</v>
+        <v>0.5636584237962202</v>
       </c>
       <c r="K12" s="4">
         <v>91.84196755625307</v>
@@ -4420,13 +4420,13 @@
         <v>7.692307692307693</v>
       </c>
       <c r="H13" s="4">
-        <v>0.5913586061274207</v>
+        <v>0.528703323580452</v>
       </c>
       <c r="I13" s="4">
-        <v>0.4168596009367159</v>
+        <v>0.2584415873607368</v>
       </c>
       <c r="J13" s="4">
-        <v>0.6641602908774539</v>
+        <v>0.5284662622426638</v>
       </c>
       <c r="K13" s="4">
         <v>90.22370486656189</v>
@@ -4470,13 +4470,13 @@
         <v>19.23076923076923</v>
       </c>
       <c r="H14" s="4">
-        <v>1.763792144953477</v>
+        <v>1.759089601099021</v>
       </c>
       <c r="I14" s="4">
         <v>1.068694591535398</v>
       </c>
       <c r="J14" s="4">
-        <v>1.778258152022378</v>
+        <v>1.771204336240694</v>
       </c>
       <c r="K14" s="4">
         <v>68.59105180533709</v>
@@ -4502,13 +4502,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>80.76923076923077</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="C15" s="3">
         <v>0</v>
       </c>
       <c r="D15" s="3">
-        <v>19.23076923076923</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -4517,16 +4517,16 @@
         <v>7.692307692307693</v>
       </c>
       <c r="G15" s="3">
-        <v>11.53846153846154</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H15" s="4">
-        <v>0.6372877228098635</v>
+        <v>0.6301177020538008</v>
       </c>
       <c r="I15" s="4">
-        <v>0.3385854790777371</v>
+        <v>0.3927219626385118</v>
       </c>
       <c r="J15" s="4">
-        <v>0.987823785723161</v>
+        <v>0.9359870661501246</v>
       </c>
       <c r="K15" s="4">
         <v>94.78806907378309</v>
@@ -4570,13 +4570,13 @@
         <v>3.846153846153846</v>
       </c>
       <c r="H16" s="4">
-        <v>1.635559199700671</v>
+        <v>1.449592705210918</v>
       </c>
       <c r="I16" s="4">
-        <v>0.9573908905643125</v>
+        <v>0.6178407623148049</v>
       </c>
       <c r="J16" s="4">
-        <v>1.63667257413143</v>
+        <v>1.371019924155178</v>
       </c>
       <c r="K16" s="4">
         <v>35.86865515436944</v>
@@ -4602,13 +4602,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="3">
-        <v>80.76923076923077</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="C17" s="3">
         <v>0</v>
       </c>
       <c r="D17" s="3">
-        <v>19.23076923076923</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -4617,16 +4617,16 @@
         <v>7.692307692307693</v>
       </c>
       <c r="G17" s="3">
-        <v>11.53846153846154</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H17" s="4">
-        <v>0.6162298982221627</v>
+        <v>0.5956766458691163</v>
       </c>
       <c r="I17" s="4">
-        <v>0.3386863408328885</v>
+        <v>0.3734200039395821</v>
       </c>
       <c r="J17" s="4">
-        <v>0.9407227473411182</v>
+        <v>0.8821492716945408</v>
       </c>
       <c r="K17" s="4">
         <v>91.89167974882238</v>
@@ -5509,13 +5509,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5">
         <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
@@ -5524,7 +5524,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -5641,13 +5641,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -5656,7 +5656,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -5905,13 +5905,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
       </c>
       <c r="D12" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5">
         <v>0</v>
@@ -5920,7 +5920,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
@@ -6037,13 +6037,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
       </c>
       <c r="D15" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5">
         <v>0</v>
@@ -6052,7 +6052,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="5">
         <v>0</v>
@@ -6125,13 +6125,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
       </c>
       <c r="D17" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="5">
         <v>0</v>
@@ -6323,22 +6323,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.085338099776988</v>
+        <v>-0.6399027876572632</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8664288909580031</v>
+        <v>0.8655656502610967</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7708967216299906</v>
+        <v>0.5387474521083391</v>
       </c>
       <c r="R3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09438903213086861</v>
+        <v>0.01917055967777515</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2203650789125004</v>
+        <v>0.2103022538593791</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2203650789125004</v>
+        <v>0.2103022538593791</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -6564,16 +6564,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9744903507753732</v>
+        <v>-0.7970815268235469</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9864014082031685</v>
+        <v>0.9701644477476208</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7947568771520118</v>
+        <v>0.7731075965446147</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -6623,16 +6623,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3527979147380279</v>
+        <v>-0.4989381982641135</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.239338620172266</v>
+        <v>0.2136953664357975</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.239338620172266</v>
+        <v>0.2136953664357975</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -6805,16 +6805,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.950875534355589</v>
+        <v>-0.3656477835478427</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7723800665873455</v>
+        <v>0.6609037000729145</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5799813315499117</v>
+        <v>0.2496722495547961</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -6864,16 +6864,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.04288700341638787</v>
+        <v>-0.1084479489704222</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.26604475306106</v>
+        <v>0.2611045565273912</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.26604475306106</v>
+        <v>0.2611045565273912</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7046,22 +7046,22 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.120751491939343</v>
+        <v>-0.7088218393050738</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7369644240562211</v>
+        <v>0.6841873789080211</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6143520543841201</v>
+        <v>0.3094469705668056</v>
       </c>
       <c r="R3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7105,16 +7105,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1094349610859467</v>
+        <v>-0.02397573230467742</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2401917390687504</v>
+        <v>0.2148439689999918</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2401917390687504</v>
+        <v>0.2148439689999918</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7287,16 +7287,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9476982320080651</v>
+        <v>-0.4752154235670218</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7794787418582416</v>
+        <v>0.6867932087592337</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.571114295536565</v>
+        <v>0.29003931525754</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1193127882426666</v>
+        <v>-0.09879441382076948</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
